--- a/docs/brands.xlsx
+++ b/docs/brands.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="183">
   <si>
     <t>slug</t>
   </si>
@@ -94,7 +94,7 @@
     <t>SEO描述</t>
   </si>
   <si>
-    <t>green-mango</t>
+    <t>demo1</t>
   </si>
   <si>
     <t>綠意芒果工坊</t>
@@ -106,7 +106,7 @@
     <t>FLOW|WITH|IT</t>
   </si>
   <si>
-    <t>屏東內埔</t>
+    <t>屏東內埔鄉</t>
   </si>
   <si>
     <t>低溫烘焙保留果香，與在地小農共製。</t>
@@ -169,7 +169,7 @@
     <t>日照香甜、低溫烘焙，與在地小農共製的芒果乾。</t>
   </si>
   <si>
-    <t>cocoa-harbor</t>
+    <t>demo2</t>
   </si>
   <si>
     <t>可可港工坊</t>
@@ -181,7 +181,7 @@
     <t>COAST|CACAO|CRAFT</t>
   </si>
   <si>
-    <t>屏東大武</t>
+    <t>屏東大武鄉</t>
   </si>
   <si>
     <t>小農合作日曬豆，低溫烘焙可可醬。</t>
@@ -242,13 +242,331 @@
   </si>
   <si>
     <t>海風日曬可可，醇厚回甘的屏東可可醬與可可豆製品。</t>
+  </si>
+  <si>
+    <t>ailiao</t>
+  </si>
+  <si>
+    <t>屏東縣內埔鄉隘寮社區發展協會</t>
+  </si>
+  <si>
+    <t>致力於將隘寮的人、文、地、產、景，打造農村魅力社區</t>
+  </si>
+  <si>
+    <t>PEOPLE | LAND | CARE</t>
+  </si>
+  <si>
+    <t>從社會照顧出發的隘寮社區發展協會，正致力於將隘寮的人、文、地、產、景，打造農村魅力社區！</t>
+  </si>
+  <si>
+    <t>黃荊舒緩膏</t>
+  </si>
+  <si>
+    <t>止癢、消腫、蚊蟲咬傷</t>
+  </si>
+  <si>
+    <t>30g/罐</t>
+  </si>
+  <si>
+    <t>防蚊貼片</t>
+  </si>
+  <si>
+    <t>純天然植物精華，有效防護蚊蟲叮咬，擁抱自然。</t>
+  </si>
+  <si>
+    <t>24入/包</t>
+  </si>
+  <si>
+    <t>在地旅行【屏東隘寮 黃荊不老村】</t>
+  </si>
+  <si>
+    <t>https://youtu.be/xFdkb2UYjjE?si=KWWkiOwE8PG9vXiC</t>
+  </si>
+  <si>
+    <t>fenggang</t>
+  </si>
+  <si>
+    <t>屏東縣枋山鄉楓港社區發展協會</t>
+  </si>
+  <si>
+    <t>結合地理特色和人文風情，發展具有在地特色的經濟活動</t>
+  </si>
+  <si>
+    <t>WIND | FRUIT | LIFE</t>
+  </si>
+  <si>
+    <t>屏東枋山鄉</t>
+  </si>
+  <si>
+    <t>協會積極推動社區產業發展，例如結合地理特色和人文風情，發展具有在地特色的經濟活動，例如結合楓港調民謠的文創產品等。</t>
+  </si>
+  <si>
+    <t>呷海楓洋蔥脆片</t>
+  </si>
+  <si>
+    <t>落山風下成長的洋蔥製成，保留鮮甜原味，風味獨具。</t>
+  </si>
+  <si>
+    <t>40g/罐</t>
+  </si>
+  <si>
+    <t>呷海楓芒果乾</t>
+  </si>
+  <si>
+    <t>海風加持的在欉黃愛文芒果，24小時二次烘焙製成，香氣濃郁撲鼻。</t>
+  </si>
+  <si>
+    <t>100g/罐</t>
+  </si>
+  <si>
+    <t>屏東縣枋山鄉楓港社區_民謠文化保存</t>
+  </si>
+  <si>
+    <t>https://youtu.be/MDJBXgHlXu4?si=5XLokf0gi3XVsfS7</t>
+  </si>
+  <si>
+    <t>xinlong</t>
+  </si>
+  <si>
+    <t>屏東縣枋寮鄉新龍社區發展協會</t>
+  </si>
+  <si>
+    <t>食漁、樂漁、慢漁</t>
+  </si>
+  <si>
+    <t>SEA | FOOD | SLOW</t>
+  </si>
+  <si>
+    <t>屏東枋寮鄉</t>
+  </si>
+  <si>
+    <t>坐擁豐富海洋的環境，提供最新鮮海鮮的口感。我們致力推廣三漁文化—食漁、樂漁、慢漁，也鼓勵訪客親身參與各式漁業活動。從走訪社區到品嚐在地美食，邀請您一同共享快樂、悠閒的「慢漁」時光。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">龍膽石斑魚粥 </t>
+  </si>
+  <si>
+    <t>4年以上飼育的龍膽石斑，慢熬釋放膠原蛋白與鮮甜，隔水加熱即可輕鬆享用。</t>
+  </si>
+  <si>
+    <t>580g/包</t>
+  </si>
+  <si>
+    <t>膠原蛋白龍膽魚湯</t>
+  </si>
+  <si>
+    <t>高蛋白、低脂肪，營養豐富且口感細膩的滋補海鮮湯品。</t>
+  </si>
+  <si>
+    <t>290g/包</t>
+  </si>
+  <si>
+    <t>屏東老家我回來啦😍帶大家體驗 以漁村為根，融合創意與觀光，翻轉過往，走出屬於自己金牌之路的枋寮新龍社區，活動內容豐富有趣👍🏾</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/HSRSb5RhwRg?si=kOHfq59oaSCstRwP</t>
+  </si>
+  <si>
+    <t>chengde</t>
+  </si>
+  <si>
+    <t>屏東縣萬巒鄉成德社區發展協會</t>
+  </si>
+  <si>
+    <t>樂天知命、安於樸實，打造「安居樂業」的未來願景</t>
+  </si>
+  <si>
+    <t>HOME | WORK | JOY</t>
+  </si>
+  <si>
+    <t>屏東萬巒鄉</t>
+  </si>
+  <si>
+    <t>成德社區是屏東萬巒的傳統農業村莊，居民世代以一級產業為生，樂天知命、安於樸實。居民齊心改善環境、保存客家文化、推動產業行銷，打造「安居樂業」的未來願景。</t>
+  </si>
+  <si>
+    <t>香檬杏仁瓦片</t>
+  </si>
+  <si>
+    <t>在地香檬結合杏仁片，酸香酥脆、風味獨特，健康又具地方特色的手作零食。</t>
+  </si>
+  <si>
+    <t>120g/罐</t>
+  </si>
+  <si>
+    <t>22度果巧克力可可醬</t>
+  </si>
+  <si>
+    <t>可可豆結合香檬發酵，果香巧克力交融，口感滑順豐富，創意甜點抹醬首選。</t>
+  </si>
+  <si>
+    <t>200g/罐</t>
+  </si>
+  <si>
+    <t>成德社區-社區老故事訪談紀錄</t>
+  </si>
+  <si>
+    <t>https://youtu.be/5yCtEUfhKLE?si=uxUHi0aF_keihMNK</t>
+  </si>
+  <si>
+    <t>chishan</t>
+  </si>
+  <si>
+    <t>屏東縣萬巒鄉赤山社區發展協會</t>
+  </si>
+  <si>
+    <t>研發鳳梨全利用，宣揚惜食永續理念，保護社區生態環境</t>
+  </si>
+  <si>
+    <t>PINEAPPLE | ZERO | WASTE</t>
+  </si>
+  <si>
+    <t>赤山位於大武山山腳下的偏遠村落，鮮少人知的一個鄉下地方，因此，期望讓赤山社區有不一樣的樣貌煥然一新。</t>
+  </si>
+  <si>
+    <t>鳳梨果乾</t>
+  </si>
+  <si>
+    <t>嚴選大武山金鑽鳳梨，無加糖保留天然香甜，與赤山小農共創純粹風味。</t>
+  </si>
+  <si>
+    <t>金鑽鳳梨活膚淨化洗面乳</t>
+  </si>
+  <si>
+    <t>金鑽鳳梨萃取搭配植物精華，溫和清潔滋潤，打造清爽不黏膩的洗面保養體驗。</t>
+  </si>
+  <si>
+    <t>150ml/瓶</t>
+  </si>
+  <si>
+    <t>萬巒鄉/社區關懷 110 0514 荒廢老屋重生 赤山社區「老厝54」成休閒好去處</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ZnBt9bodZxw?si=2YnhmfoULMYbKJUw</t>
+  </si>
+  <si>
+    <t>wandan</t>
+  </si>
+  <si>
+    <t>萬丹鄉農會</t>
+  </si>
+  <si>
+    <t>土地平闊，地質肥沃，水利充足，人民富裕</t>
+  </si>
+  <si>
+    <t>RICH | LAND | FARM</t>
+  </si>
+  <si>
+    <t>屏東萬丹鄉</t>
+  </si>
+  <si>
+    <t>萬丹鄉位於屏東平原南部，土地平闊，地質肥沃，水利充足，人民富裕，在本縣是生活水準頗高的地方，地形主要以平原為主，肥沃的土壤和豐沛的地下水源，使本鄉成為屏東縣境內的農產之鄉</t>
+  </si>
+  <si>
+    <t>紅豆豆奶</t>
+  </si>
+  <si>
+    <t>嚴選台灣萬丹紅豆泥，非基改無添加，安全健康，風味濃郁純粹。</t>
+  </si>
+  <si>
+    <t>300ml/罐</t>
+  </si>
+  <si>
+    <t>黑米紅豆粥</t>
+  </si>
+  <si>
+    <t>富膳食纖維與花青素及多種微量元素，紅豆黑米香濃甜綿，濃稠鬆軟，冰熱飲皆適宜。</t>
+  </si>
+  <si>
+    <t>250g/罐</t>
+  </si>
+  <si>
+    <t>2025屏東萬丹紅豆牛奶節！ 一起烙印紅豆餅同歡</t>
+  </si>
+  <si>
+    <t>https://youtu.be/nYNV0MAjHYo?si=2wAiZTTnbCZ6Obep</t>
+  </si>
+  <si>
+    <t>pingtung</t>
+  </si>
+  <si>
+    <t>屏東縣農會</t>
+  </si>
+  <si>
+    <t>台灣國境之南，境內氣候宜人四季如春，以農業及觀光為發展主力</t>
+  </si>
+  <si>
+    <t>SOUTH | FARM | TRAVEL</t>
+  </si>
+  <si>
+    <t>屏東市</t>
+  </si>
+  <si>
+    <t>屏東縣，台灣國境之南，境內氣候宜人四季如春，是以農業及觀光為發展主力的大縣，北與高雄市為界，地處熱帶地區，富有濃厚熱帶風情。地方農產豐富。</t>
+  </si>
+  <si>
+    <t>屏縣農紅豆湯</t>
+  </si>
+  <si>
+    <t>紅豆顆粒飽滿細緻綿密，傳統工法製成，甜度適中，展現道地古早味。</t>
+  </si>
+  <si>
+    <t>320g/罐</t>
+  </si>
+  <si>
+    <t>屏縣農蜜黑豆真空包裝1盒</t>
+  </si>
+  <si>
+    <t>高雄七號黑豆，富植物蛋白與維生素，口感Q彈，古法熬煮，拆封即食美味傳承。</t>
+  </si>
+  <si>
+    <t>300g/包</t>
+  </si>
+  <si>
+    <t>20250829炎夏消暑 屏東縣農會推隱藏版鮮果冰品</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ECve-Fmw3KA?si=azVJZ2A-EPMinkAb</t>
+  </si>
+  <si>
+    <t>jiadong</t>
+  </si>
+  <si>
+    <t>佳冬鄉農會</t>
+  </si>
+  <si>
+    <t>以蓮霧種植和農村體驗為特色，積極推廣「透紅佳人」蓮霧品牌</t>
+  </si>
+  <si>
+    <t>WAXAPPLE | RED | SWEET</t>
+  </si>
+  <si>
+    <t>屏東佳冬鄉</t>
+  </si>
+  <si>
+    <t>佳冬鄉農會一個以蓮霧種植和農村體驗為特色的農會。 農會推廣的「透紅佳人」蓮霧品牌，以其高品質和穩定的產量聞名，並成功拓展到國際市場。 此外，佳冬鄉農會也積極發展農村體驗活動，將在地人文與農遊結合，讓遊客體驗客庄風情與文化。</t>
+  </si>
+  <si>
+    <t>蓮霧果乾</t>
+  </si>
+  <si>
+    <t>低溫烘燥留住蓮霧新鮮的好滋味。清甜爽口，含有淡淡果乾香。當成零嘴健康又無負擔！</t>
+  </si>
+  <si>
+    <t>50g/包</t>
+  </si>
+  <si>
+    <t>佳冬鄉農會 透紅佳人園區｜食農教育向前行</t>
+  </si>
+  <si>
+    <t>https://youtu.be/e4sKwAUKikw?si=ptUqEFrBj93A0B5p</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -258,27 +576,60 @@
     <font>
       <b/>
       <sz val="12.0"/>
-      <color rgb="FF000000"/>
-      <name val="新細明體"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12.0"/>
-      <color rgb="FF000000"/>
-      <name val="新細明體"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="12.0"/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
-      <name val="新細明體"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12.0"/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color theme="1"/>
+      <name val="Heiti TC"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor rgb="FFF8F9FA"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -287,29 +638,108 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2">
+    <tableStyle count="2" pivot="0" name="工作表1-style">
+      <tableStyleElement dxfId="1" type="firstRowStripe"/>
+      <tableStyleElement dxfId="2" type="secondRowStripe"/>
+    </tableStyle>
+    <tableStyle count="2" pivot="0" name="工作表1-style 2">
+      <tableStyleElement dxfId="1" type="firstRowStripe"/>
+      <tableStyleElement dxfId="2" type="secondRowStripe"/>
+    </tableStyle>
+  </tableStyles>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="B5:D29" displayName="Table_1" name="Table_1" id="1">
+  <tableColumns count="3">
+    <tableColumn name="Column1" id="1"/>
+    <tableColumn name="Column2" id="2"/>
+    <tableColumn name="Column3" id="3"/>
+  </tableColumns>
+  <tableStyleInfo name="工作表1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="Z5:AA11" displayName="Table_2" name="Table_2" id="2">
+  <tableColumns count="2">
+    <tableColumn name="Column1" id="1"/>
+    <tableColumn name="Column2" id="2"/>
+  </tableColumns>
+  <tableStyleInfo name="工作表1-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -512,6 +942,19 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="32.38"/>
+    <col customWidth="1" min="3" max="3" width="38.0"/>
+    <col customWidth="1" min="4" max="4" width="26.63"/>
+    <col customWidth="1" min="5" max="5" width="14.13"/>
+    <col customWidth="1" min="6" max="6" width="134.88"/>
+    <col customWidth="1" min="10" max="10" width="14.5"/>
+    <col customWidth="1" min="11" max="11" width="78.75"/>
+    <col customWidth="1" min="12" max="12" width="10.38"/>
+    <col customWidth="1" min="13" max="13" width="10.63"/>
+    <col customWidth="1" min="16" max="16" width="16.5"/>
+    <col customWidth="1" min="17" max="17" width="75.13"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -603,25 +1046,25 @@
       <c r="B2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="5" t="s">
         <v>33</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="5" t="s">
         <v>35</v>
       </c>
       <c r="J2" s="2" t="s">
@@ -636,10 +1079,10 @@
       <c r="M2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="5" t="s">
         <v>40</v>
       </c>
       <c r="P2" s="2" t="s">
@@ -654,16 +1097,16 @@
       <c r="S2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="T2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="U2" s="5" t="s">
         <v>45</v>
       </c>
       <c r="V2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="W2" s="5" t="s">
         <v>47</v>
       </c>
       <c r="X2" s="2" t="s">
@@ -686,25 +1129,25 @@
       <c r="B3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="5" t="s">
         <v>58</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="5" t="s">
         <v>60</v>
       </c>
       <c r="J3" s="2" t="s">
@@ -719,10 +1162,10 @@
       <c r="M3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="5" t="s">
         <v>65</v>
       </c>
       <c r="P3" s="2" t="s">
@@ -737,16 +1180,16 @@
       <c r="S3" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="T3" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="U3" s="5" t="s">
         <v>70</v>
       </c>
       <c r="V3" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="W3" s="5" t="s">
         <v>72</v>
       </c>
       <c r="X3" s="2" t="s">
@@ -761,6 +1204,614 @@
       <c r="AA3" s="2" t="s">
         <v>76</v>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L4" s="4">
+        <v>200.0</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="R4" s="4">
+        <v>250.0</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="W4" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA4" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="L5" s="4">
+        <v>70.0</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="R5" s="4">
+        <v>160.0</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="W5" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA5" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="L6" s="4">
+        <v>300.0</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="R6" s="4">
+        <v>150.0</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="W6" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="X6" s="10"/>
+      <c r="Y6" s="10"/>
+      <c r="Z6" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L7" s="4">
+        <v>200.0</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="R7" s="4">
+        <v>400.0</v>
+      </c>
+      <c r="S7" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="W7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA7" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="L8" s="4">
+        <v>150.0</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="R8" s="4">
+        <v>230.0</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="W8" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="X8" s="10"/>
+      <c r="Y8" s="10"/>
+      <c r="Z8" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA8" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="L9" s="4">
+        <v>38.0</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="R9" s="4">
+        <v>38.0</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="W9" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="10"/>
+      <c r="Z9" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA9" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L10" s="4">
+        <v>45.0</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="R10" s="4">
+        <v>120.0</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="W10" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10"/>
+      <c r="Z10" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA10" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L11" s="4">
+        <v>200.0</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="W11" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10"/>
+      <c r="Z11" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA11" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="10"/>
+      <c r="Z12" s="10"/>
+      <c r="AA12" s="10"/>
+    </row>
+    <row r="13">
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+    </row>
+    <row r="15">
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+    </row>
+    <row r="16">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+    </row>
+    <row r="21">
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+    </row>
+    <row r="22">
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+    </row>
+    <row r="26">
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+    </row>
+    <row r="28">
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -778,7 +1829,19 @@
     <hyperlink r:id="rId12" ref="T3"/>
     <hyperlink r:id="rId13" ref="U3"/>
     <hyperlink r:id="rId14" ref="W3"/>
+    <hyperlink r:id="rId15" ref="W4"/>
+    <hyperlink r:id="rId16" ref="W5"/>
+    <hyperlink r:id="rId17" ref="W6"/>
+    <hyperlink r:id="rId18" ref="W7"/>
+    <hyperlink r:id="rId19" ref="W8"/>
+    <hyperlink r:id="rId20" ref="W9"/>
+    <hyperlink r:id="rId21" ref="W10"/>
+    <hyperlink r:id="rId22" ref="W11"/>
   </hyperlinks>
-  <drawing r:id="rId15"/>
+  <drawing r:id="rId23"/>
+  <tableParts count="2">
+    <tablePart r:id="rId26"/>
+    <tablePart r:id="rId27"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/docs/brands.xlsx
+++ b/docs/brands.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="198">
   <si>
     <t>slug</t>
   </si>
@@ -268,6 +268,9 @@
     <t>30g/罐</t>
   </si>
   <si>
+    <t>../../public/assets/ailiao/B_１_1.png</t>
+  </si>
+  <si>
     <t>防蚊貼片</t>
   </si>
   <si>
@@ -277,6 +280,9 @@
     <t>24入/包</t>
   </si>
   <si>
+    <t>../../public/assets/ailiao/B_１_２.png</t>
+  </si>
+  <si>
     <t>在地旅行【屏東隘寮 黃荊不老村】</t>
   </si>
   <si>
@@ -310,6 +316,9 @@
     <t>40g/罐</t>
   </si>
   <si>
+    <t>../../public/assets/fenggang/B_２_1.png</t>
+  </si>
+  <si>
     <t>呷海楓芒果乾</t>
   </si>
   <si>
@@ -319,6 +328,9 @@
     <t>100g/罐</t>
   </si>
   <si>
+    <t>../../public/assets/fenggang/B_２_２.png</t>
+  </si>
+  <si>
     <t>屏東縣枋山鄉楓港社區_民謠文化保存</t>
   </si>
   <si>
@@ -352,6 +364,9 @@
     <t>580g/包</t>
   </si>
   <si>
+    <t>../../public/assets/xinlong/B_３_1.png</t>
+  </si>
+  <si>
     <t>膠原蛋白龍膽魚湯</t>
   </si>
   <si>
@@ -361,6 +376,9 @@
     <t>290g/包</t>
   </si>
   <si>
+    <t>../../public/assets/xinlong/B_３_２.png</t>
+  </si>
+  <si>
     <t>屏東老家我回來啦😍帶大家體驗 以漁村為根，融合創意與觀光，翻轉過往，走出屬於自己金牌之路的枋寮新龍社區，活動內容豐富有趣👍🏾</t>
   </si>
   <si>
@@ -394,6 +412,9 @@
     <t>120g/罐</t>
   </si>
   <si>
+    <t>../../public/assets/chengde/B_４_1.png</t>
+  </si>
+  <si>
     <t>22度果巧克力可可醬</t>
   </si>
   <si>
@@ -403,6 +424,9 @@
     <t>200g/罐</t>
   </si>
   <si>
+    <t>../../public/assets/chengde/B_４_２.png</t>
+  </si>
+  <si>
     <t>成德社區-社區老故事訪談紀錄</t>
   </si>
   <si>
@@ -430,6 +454,9 @@
     <t>嚴選大武山金鑽鳳梨，無加糖保留天然香甜，與赤山小農共創純粹風味。</t>
   </si>
   <si>
+    <t>../../public/assets/chishan/B_５_1.png</t>
+  </si>
+  <si>
     <t>金鑽鳳梨活膚淨化洗面乳</t>
   </si>
   <si>
@@ -439,6 +466,9 @@
     <t>150ml/瓶</t>
   </si>
   <si>
+    <t>../../public/assets/chishan/B_５_２.png</t>
+  </si>
+  <si>
     <t>萬巒鄉/社區關懷 110 0514 荒廢老屋重生 赤山社區「老厝54」成休閒好去處</t>
   </si>
   <si>
@@ -472,6 +502,9 @@
     <t>300ml/罐</t>
   </si>
   <si>
+    <t>../../public/assets/wandan/B_6_1.png</t>
+  </si>
+  <si>
     <t>黑米紅豆粥</t>
   </si>
   <si>
@@ -481,6 +514,9 @@
     <t>250g/罐</t>
   </si>
   <si>
+    <t>../../public/assets/wandan/B_6_２.png</t>
+  </si>
+  <si>
     <t>2025屏東萬丹紅豆牛奶節！ 一起烙印紅豆餅同歡</t>
   </si>
   <si>
@@ -514,6 +550,9 @@
     <t>320g/罐</t>
   </si>
   <si>
+    <t>../../public/assets/pingtung/B_7_1.png</t>
+  </si>
+  <si>
     <t>屏縣農蜜黑豆真空包裝1盒</t>
   </si>
   <si>
@@ -523,6 +562,9 @@
     <t>300g/包</t>
   </si>
   <si>
+    <t>../../public/assets/pingtung/B_7_２.png</t>
+  </si>
+  <si>
     <t>20250829炎夏消暑 屏東縣農會推隱藏版鮮果冰品</t>
   </si>
   <si>
@@ -554,6 +596,9 @@
   </si>
   <si>
     <t>50g/包</t>
+  </si>
+  <si>
+    <t>../../public/assets/jiadong/B_8_1.png</t>
   </si>
   <si>
     <t>佳冬鄉農會 透紅佳人園區｜食農教育向前行</t>
@@ -952,8 +997,11 @@
     <col customWidth="1" min="11" max="11" width="78.75"/>
     <col customWidth="1" min="12" max="12" width="10.38"/>
     <col customWidth="1" min="13" max="13" width="10.63"/>
+    <col customWidth="1" min="14" max="14" width="52.88"/>
+    <col customWidth="1" min="15" max="15" width="20.38"/>
     <col customWidth="1" min="16" max="16" width="16.5"/>
     <col customWidth="1" min="17" max="17" width="75.13"/>
+    <col customWidth="1" min="20" max="20" width="49.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1239,27 +1287,31 @@
       <c r="M4" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="N4" s="2"/>
+      <c r="N4" s="4" t="s">
+        <v>85</v>
+      </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R4" s="4">
         <v>250.0</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="T4" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>89</v>
+      </c>
       <c r="U4" s="2"/>
       <c r="V4" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="W4" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="X4" s="2"/>
       <c r="Y4" s="2"/>
@@ -1272,226 +1324,238 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
       <c r="J5" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L5" s="4">
         <v>70.0</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="N5" s="10"/>
+        <v>100</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="O5" s="10"/>
       <c r="P5" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="R5" s="4">
         <v>160.0</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="T5" s="10"/>
+        <v>104</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>105</v>
+      </c>
       <c r="U5" s="10"/>
       <c r="V5" s="8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="W5" s="9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="X5" s="10"/>
       <c r="Y5" s="10"/>
       <c r="Z5" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AA5" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="L6" s="4">
         <v>300.0</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="N6" s="10"/>
+        <v>116</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>117</v>
+      </c>
       <c r="O6" s="10"/>
       <c r="P6" s="10" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="R6" s="4">
         <v>150.0</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="T6" s="10"/>
+        <v>120</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>121</v>
+      </c>
       <c r="U6" s="10"/>
       <c r="V6" s="8" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="W6" s="9" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="X6" s="10"/>
       <c r="Y6" s="10"/>
       <c r="Z6" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="L7" s="4">
         <v>200.0</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="N7" s="10"/>
+        <v>132</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>133</v>
+      </c>
       <c r="O7" s="10"/>
       <c r="P7" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="R7" s="4">
         <v>400.0</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="T7" s="10"/>
+        <v>136</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="U7" s="10"/>
       <c r="V7" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="W7" s="9" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="X7" s="10"/>
       <c r="Y7" s="10"/>
       <c r="Z7" s="10" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="AA7" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L8" s="4">
         <v>150.0</v>
@@ -1499,218 +1563,232 @@
       <c r="M8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="N8" s="10"/>
+      <c r="N8" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="O8" s="10"/>
       <c r="P8" s="10" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="R8" s="4">
         <v>230.0</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="T8" s="10"/>
+        <v>150</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>151</v>
+      </c>
       <c r="U8" s="10"/>
       <c r="V8" s="8" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="W8" s="9" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="X8" s="10"/>
       <c r="Y8" s="10"/>
       <c r="Z8" s="10" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="AA8" s="6" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="L9" s="4">
         <v>38.0</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="N9" s="10"/>
+        <v>162</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>163</v>
+      </c>
       <c r="O9" s="10"/>
       <c r="P9" s="10" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="R9" s="4">
         <v>38.0</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="T9" s="10"/>
+        <v>166</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>167</v>
+      </c>
       <c r="U9" s="10"/>
       <c r="V9" s="8" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="W9" s="9" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="X9" s="10"/>
       <c r="Y9" s="10"/>
       <c r="Z9" s="10" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="AA9" s="6" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="L10" s="4">
         <v>45.0</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="N10" s="10"/>
+        <v>178</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>179</v>
+      </c>
       <c r="O10" s="10"/>
       <c r="P10" s="10" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="R10" s="4">
         <v>120.0</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="T10" s="10"/>
+        <v>182</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>183</v>
+      </c>
       <c r="U10" s="10"/>
       <c r="V10" s="8" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="W10" s="9" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="X10" s="10"/>
       <c r="Y10" s="10"/>
       <c r="Z10" s="10" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AA10" s="6" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="L11" s="4">
         <v>200.0</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="N11" s="10"/>
+        <v>194</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>195</v>
+      </c>
       <c r="O11" s="10"/>
       <c r="T11" s="10"/>
       <c r="U11" s="10"/>
       <c r="V11" s="8" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="W11" s="9" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="X11" s="10"/>
       <c r="Y11" s="10"/>
       <c r="Z11" s="10" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="AA11" s="6" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">

--- a/docs/brands.xlsx
+++ b/docs/brands.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="207">
   <si>
     <t>slug</t>
   </si>
@@ -19,6 +19,9 @@
     <t>品牌名稱</t>
   </si>
   <si>
+    <t>Logo</t>
+  </si>
+  <si>
     <t>標語</t>
   </si>
   <si>
@@ -250,6 +253,9 @@
     <t>屏東縣內埔鄉隘寮社區發展協會</t>
   </si>
   <si>
+    <t>L1.png</t>
+  </si>
+  <si>
     <t>致力於將隘寮的人、文、地、產、景，打造農村魅力社區</t>
   </si>
   <si>
@@ -268,7 +274,7 @@
     <t>30g/罐</t>
   </si>
   <si>
-    <t>../../public/assets/ailiao/B_１_1.png</t>
+    <t>B_１_1.png</t>
   </si>
   <si>
     <t>防蚊貼片</t>
@@ -295,6 +301,9 @@
     <t>屏東縣枋山鄉楓港社區發展協會</t>
   </si>
   <si>
+    <t>L2.jpeg</t>
+  </si>
+  <si>
     <t>結合地理特色和人文風情，發展具有在地特色的經濟活動</t>
   </si>
   <si>
@@ -316,7 +325,7 @@
     <t>40g/罐</t>
   </si>
   <si>
-    <t>../../public/assets/fenggang/B_２_1.png</t>
+    <t>B_２_1.png</t>
   </si>
   <si>
     <t>呷海楓芒果乾</t>
@@ -343,6 +352,9 @@
     <t>屏東縣枋寮鄉新龍社區發展協會</t>
   </si>
   <si>
+    <t>L3.jpg</t>
+  </si>
+  <si>
     <t>食漁、樂漁、慢漁</t>
   </si>
   <si>
@@ -364,7 +376,7 @@
     <t>580g/包</t>
   </si>
   <si>
-    <t>../../public/assets/xinlong/B_３_1.png</t>
+    <t>B_３_1.png</t>
   </si>
   <si>
     <t>膠原蛋白龍膽魚湯</t>
@@ -391,6 +403,9 @@
     <t>屏東縣萬巒鄉成德社區發展協會</t>
   </si>
   <si>
+    <t>L4.png</t>
+  </si>
+  <si>
     <t>樂天知命、安於樸實，打造「安居樂業」的未來願景</t>
   </si>
   <si>
@@ -412,7 +427,7 @@
     <t>120g/罐</t>
   </si>
   <si>
-    <t>../../public/assets/chengde/B_４_1.png</t>
+    <t>B_４_1.png</t>
   </si>
   <si>
     <t>22度果巧克力可可醬</t>
@@ -439,6 +454,9 @@
     <t>屏東縣萬巒鄉赤山社區發展協會</t>
   </si>
   <si>
+    <t>L5.jpg</t>
+  </si>
+  <si>
     <t>研發鳳梨全利用，宣揚惜食永續理念，保護社區生態環境</t>
   </si>
   <si>
@@ -454,7 +472,7 @@
     <t>嚴選大武山金鑽鳳梨，無加糖保留天然香甜，與赤山小農共創純粹風味。</t>
   </si>
   <si>
-    <t>../../public/assets/chishan/B_５_1.png</t>
+    <t>B_５_1.png</t>
   </si>
   <si>
     <t>金鑽鳳梨活膚淨化洗面乳</t>
@@ -481,6 +499,9 @@
     <t>萬丹鄉農會</t>
   </si>
   <si>
+    <t>L6.jpg</t>
+  </si>
+  <si>
     <t>土地平闊，地質肥沃，水利充足，人民富裕</t>
   </si>
   <si>
@@ -502,7 +523,7 @@
     <t>300ml/罐</t>
   </si>
   <si>
-    <t>../../public/assets/wandan/B_6_1.png</t>
+    <t>B_6_1.png</t>
   </si>
   <si>
     <t>黑米紅豆粥</t>
@@ -529,6 +550,9 @@
     <t>屏東縣農會</t>
   </si>
   <si>
+    <t>L7.jpg</t>
+  </si>
+  <si>
     <t>台灣國境之南，境內氣候宜人四季如春，以農業及觀光為發展主力</t>
   </si>
   <si>
@@ -550,7 +574,7 @@
     <t>320g/罐</t>
   </si>
   <si>
-    <t>../../public/assets/pingtung/B_7_1.png</t>
+    <t>B_7_1.png</t>
   </si>
   <si>
     <t>屏縣農蜜黑豆真空包裝1盒</t>
@@ -577,6 +601,9 @@
     <t>佳冬鄉農會</t>
   </si>
   <si>
+    <t>L8.png</t>
+  </si>
+  <si>
     <t>以蓮霧種植和農村體驗為特色，積極推廣「透紅佳人」蓮霧品牌</t>
   </si>
   <si>
@@ -598,7 +625,7 @@
     <t>50g/包</t>
   </si>
   <si>
-    <t>../../public/assets/jiadong/B_8_1.png</t>
+    <t>B_8_1.png</t>
   </si>
   <si>
     <t>佳冬鄉農會 透紅佳人園區｜食農教育向前行</t>
@@ -647,14 +674,14 @@
       <color rgb="FF0000FF"/>
     </font>
     <font>
+      <u/>
+      <sz val="12.0"/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color theme="1"/>
-      <name val="Heiti TC"/>
     </font>
   </fonts>
   <fills count="4">
@@ -672,8 +699,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8F9FA"/>
-        <bgColor rgb="FFF8F9FA"/>
+        <fgColor rgb="FFF3F3F3"/>
+        <bgColor rgb="FFF3F3F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -683,11 +710,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
@@ -708,14 +738,25 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -767,18 +808,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="B5:D29" displayName="Table_1" name="Table_1" id="1">
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="B5:E11" displayName="Table_1" name="Table_1" id="1">
+  <tableColumns count="4">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
     <tableColumn name="Column3" id="3"/>
+    <tableColumn name="Column4" id="4"/>
   </tableColumns>
   <tableStyleInfo name="工作表1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="Z5:AA11" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="AA5:AB11" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="2">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -988,20 +1030,20 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="32.38"/>
-    <col customWidth="1" min="3" max="3" width="38.0"/>
-    <col customWidth="1" min="4" max="4" width="26.63"/>
-    <col customWidth="1" min="5" max="5" width="14.13"/>
-    <col customWidth="1" min="6" max="6" width="134.88"/>
-    <col customWidth="1" min="10" max="10" width="14.5"/>
-    <col customWidth="1" min="11" max="11" width="78.75"/>
-    <col customWidth="1" min="12" max="12" width="10.38"/>
-    <col customWidth="1" min="13" max="13" width="10.63"/>
-    <col customWidth="1" min="14" max="14" width="52.88"/>
-    <col customWidth="1" min="15" max="15" width="20.38"/>
-    <col customWidth="1" min="16" max="16" width="16.5"/>
-    <col customWidth="1" min="17" max="17" width="75.13"/>
-    <col customWidth="1" min="20" max="20" width="49.88"/>
+    <col customWidth="1" min="2" max="3" width="32.38"/>
+    <col customWidth="1" min="4" max="4" width="38.0"/>
+    <col customWidth="1" min="5" max="5" width="26.63"/>
+    <col customWidth="1" min="6" max="6" width="14.13"/>
+    <col customWidth="1" min="7" max="7" width="134.88"/>
+    <col customWidth="1" min="11" max="11" width="14.5"/>
+    <col customWidth="1" min="12" max="12" width="78.75"/>
+    <col customWidth="1" min="13" max="13" width="10.38"/>
+    <col customWidth="1" min="14" max="14" width="10.63"/>
+    <col customWidth="1" min="15" max="15" width="52.88"/>
+    <col customWidth="1" min="16" max="16" width="20.38"/>
+    <col customWidth="1" min="17" max="17" width="16.5"/>
+    <col customWidth="1" min="18" max="18" width="75.13"/>
+    <col customWidth="1" min="21" max="21" width="49.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1011,7 +1053,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1086,835 +1128,768 @@
       <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="3">
         <v>220.0</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" s="3">
         <v>180.0</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T2" s="5" t="s">
+      <c r="T2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="U2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="W2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AA2" s="3" t="s">
         <v>51</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M3" s="3">
         <v>250.0</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="S3" s="3">
         <v>190.0</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="T3" s="5" t="s">
+      <c r="T3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="U3" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V3" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="W3" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X3" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Y3" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="Z3" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AA3" s="3" t="s">
         <v>76</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="F4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="L4" s="4">
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M4" s="5">
         <v>200.0</v>
       </c>
-      <c r="M4" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="s">
+      <c r="N4" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="O4" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="R4" s="4">
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="S4" s="5">
         <v>250.0</v>
       </c>
-      <c r="S4" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="U4" s="2"/>
-      <c r="V4" s="8" t="s">
+      <c r="T4" s="5" t="s">
         <v>90</v>
       </c>
+      <c r="U4" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="V4" s="3"/>
       <c r="W4" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA4" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="X4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3" t="s">
         <v>79</v>
+      </c>
+      <c r="AB4" s="7" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="A5" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="B5" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="C5" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="D5" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10" t="s">
+      <c r="E5" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="F5" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L5" s="4">
+      <c r="G5" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="M5" s="13">
         <v>70.0</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q5" s="2" t="s">
+      <c r="N5" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="R5" s="4">
+      <c r="O5" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="S5" s="13">
         <v>160.0</v>
       </c>
-      <c r="S5" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="U5" s="10"/>
-      <c r="V5" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="W5" s="9" t="s">
+      <c r="T5" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="X5" s="10"/>
-      <c r="Y5" s="10"/>
-      <c r="Z5" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="AA5" s="6" t="s">
-        <v>94</v>
+      <c r="U5" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="V5" s="12"/>
+      <c r="W5" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="X5" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="12"/>
+      <c r="AA5" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB5" s="14" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="11" t="s">
+      <c r="A6" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="B6" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10" t="s">
+      <c r="D6" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="E6" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="L6" s="4">
+      <c r="F6" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M6" s="5">
         <v>300.0</v>
       </c>
-      <c r="M6" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="R6" s="4">
+      <c r="N6" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="S6" s="5">
         <v>150.0</v>
       </c>
-      <c r="S6" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="T6" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="U6" s="10"/>
-      <c r="V6" s="8" t="s">
-        <v>122</v>
-      </c>
+      <c r="T6" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="U6" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="V6" s="17"/>
       <c r="W6" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="X6" s="10"/>
-      <c r="Y6" s="10"/>
-      <c r="Z6" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA6" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
+      </c>
+      <c r="X6" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y6" s="17"/>
+      <c r="Z6" s="17"/>
+      <c r="AA6" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB6" s="4" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="A7" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="B7" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10" t="s">
+      <c r="C7" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="D7" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="L7" s="4">
+      <c r="E7" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="M7" s="13">
         <v>200.0</v>
       </c>
-      <c r="M7" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="O7" s="10"/>
-      <c r="P7" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="R7" s="4">
+      <c r="N7" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="R7" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="S7" s="13">
         <v>400.0</v>
       </c>
-      <c r="S7" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="T7" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="U7" s="10"/>
-      <c r="V7" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="W7" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="X7" s="10"/>
-      <c r="Y7" s="10"/>
-      <c r="Z7" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA7" s="6" t="s">
-        <v>126</v>
+      <c r="T7" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U7" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="V7" s="12"/>
+      <c r="W7" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="X7" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12"/>
+      <c r="AA7" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB7" s="14" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10" t="s">
+      <c r="A8" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="B8" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="L8" s="4">
+      <c r="C8" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="M8" s="5">
         <v>150.0</v>
       </c>
-      <c r="M8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10" t="s">
+      <c r="N8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="S8" s="5">
+        <v>230.0</v>
+      </c>
+      <c r="T8" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="U8" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="V8" s="17"/>
+      <c r="W8" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="X8" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="17"/>
+      <c r="AA8" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB8" s="7" t="s">
         <v>148</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="R8" s="4">
-        <v>230.0</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="T8" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="U8" s="10"/>
-      <c r="V8" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="W8" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="X8" s="10"/>
-      <c r="Y8" s="10"/>
-      <c r="Z8" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="AA8" s="6" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10" t="s">
+      <c r="A9" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="B9" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="L9" s="4">
+      <c r="C9" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="M9" s="13">
         <v>38.0</v>
       </c>
-      <c r="M9" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="N9" s="4" t="s">
+      <c r="N9" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="R9" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="S9" s="13">
+        <v>38.0</v>
+      </c>
+      <c r="T9" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="U9" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="V9" s="12"/>
+      <c r="W9" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="X9" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="Y9" s="12"/>
+      <c r="Z9" s="12"/>
+      <c r="AA9" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB9" s="14" t="s">
         <v>163</v>
-      </c>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="R9" s="4">
-        <v>38.0</v>
-      </c>
-      <c r="S9" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="T9" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="U9" s="10"/>
-      <c r="V9" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="W9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="X9" s="10"/>
-      <c r="Y9" s="10"/>
-      <c r="Z9" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA9" s="6" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="K10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="L10" s="4">
+      <c r="B10" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="M10" s="5">
         <v>45.0</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="N10" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="S10" s="5">
+        <v>120.0</v>
+      </c>
+      <c r="T10" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="U10" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="V10" s="17"/>
+      <c r="W10" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="X10" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="17"/>
+      <c r="AA10" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="N10" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10" t="s">
+      <c r="AB10" s="7" t="s">
         <v>180</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="R10" s="4">
-        <v>120.0</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="T10" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="U10" s="10"/>
-      <c r="V10" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="W10" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="X10" s="10"/>
-      <c r="Y10" s="10"/>
-      <c r="Z10" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="AA10" s="6" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="L11" s="4">
+      <c r="A11" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="M11" s="13">
         <v>200.0</v>
       </c>
-      <c r="M11" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="O11" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="12"/>
+      <c r="V11" s="12"/>
+      <c r="W11" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="X11" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y11" s="12"/>
+      <c r="Z11" s="12"/>
+      <c r="AA11" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="O11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="W11" s="9" t="s">
+      <c r="AB11" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="X11" s="10"/>
-      <c r="Y11" s="10"/>
-      <c r="Z11" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="AA11" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
-      <c r="V12" s="10"/>
-      <c r="W12" s="10"/>
-      <c r="X12" s="10"/>
-      <c r="Y12" s="10"/>
-      <c r="Z12" s="10"/>
-      <c r="AA12" s="10"/>
-    </row>
-    <row r="13">
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-    </row>
-    <row r="15">
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-    </row>
-    <row r="16">
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-    </row>
-    <row r="17">
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-    </row>
-    <row r="21">
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-    </row>
-    <row r="22">
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-    </row>
-    <row r="25">
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-    </row>
-    <row r="26">
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-    </row>
-    <row r="27">
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-    </row>
-    <row r="28">
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="G2"/>
-    <hyperlink r:id="rId2" ref="I2"/>
-    <hyperlink r:id="rId3" ref="N2"/>
-    <hyperlink r:id="rId4" ref="O2"/>
-    <hyperlink r:id="rId5" ref="T2"/>
-    <hyperlink r:id="rId6" ref="U2"/>
-    <hyperlink r:id="rId7" ref="W2"/>
-    <hyperlink r:id="rId8" ref="G3"/>
-    <hyperlink r:id="rId9" ref="I3"/>
-    <hyperlink r:id="rId10" ref="N3"/>
-    <hyperlink r:id="rId11" ref="O3"/>
-    <hyperlink r:id="rId12" ref="T3"/>
-    <hyperlink r:id="rId13" ref="U3"/>
-    <hyperlink r:id="rId14" ref="W3"/>
-    <hyperlink r:id="rId15" ref="W4"/>
-    <hyperlink r:id="rId16" ref="W5"/>
-    <hyperlink r:id="rId17" ref="W6"/>
-    <hyperlink r:id="rId18" ref="W7"/>
-    <hyperlink r:id="rId19" ref="W8"/>
-    <hyperlink r:id="rId20" ref="W9"/>
-    <hyperlink r:id="rId21" ref="W10"/>
-    <hyperlink r:id="rId22" ref="W11"/>
+    <hyperlink r:id="rId1" ref="H2"/>
+    <hyperlink r:id="rId2" ref="J2"/>
+    <hyperlink r:id="rId3" ref="O2"/>
+    <hyperlink r:id="rId4" ref="P2"/>
+    <hyperlink r:id="rId5" ref="U2"/>
+    <hyperlink r:id="rId6" ref="V2"/>
+    <hyperlink r:id="rId7" ref="X2"/>
+    <hyperlink r:id="rId8" ref="H3"/>
+    <hyperlink r:id="rId9" ref="J3"/>
+    <hyperlink r:id="rId10" ref="O3"/>
+    <hyperlink r:id="rId11" ref="P3"/>
+    <hyperlink r:id="rId12" ref="U3"/>
+    <hyperlink r:id="rId13" ref="V3"/>
+    <hyperlink r:id="rId14" ref="X3"/>
+    <hyperlink r:id="rId15" ref="X4"/>
+    <hyperlink r:id="rId16" ref="X5"/>
+    <hyperlink r:id="rId17" ref="X6"/>
+    <hyperlink r:id="rId18" ref="X7"/>
+    <hyperlink r:id="rId19" ref="X8"/>
+    <hyperlink r:id="rId20" ref="X9"/>
+    <hyperlink r:id="rId21" ref="X10"/>
+    <hyperlink r:id="rId22" ref="X11"/>
   </hyperlinks>
   <drawing r:id="rId23"/>
   <tableParts count="2">

--- a/docs/brands.xlsx
+++ b/docs/brands.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="216">
   <si>
     <t>slug</t>
   </si>
@@ -22,6 +22,9 @@
     <t>Logo</t>
   </si>
   <si>
+    <t>Hero Image</t>
+  </si>
+  <si>
     <t>標語</t>
   </si>
   <si>
@@ -256,6 +259,9 @@
     <t>L1.png</t>
   </si>
   <si>
+    <t>H1.webp</t>
+  </si>
+  <si>
     <t>致力於將隘寮的人、文、地、產、景，打造農村魅力社區</t>
   </si>
   <si>
@@ -304,6 +310,9 @@
     <t>L2.jpeg</t>
   </si>
   <si>
+    <t>H2.jpg</t>
+  </si>
+  <si>
     <t>結合地理特色和人文風情，發展具有在地特色的經濟活動</t>
   </si>
   <si>
@@ -355,6 +364,9 @@
     <t>L3.jpg</t>
   </si>
   <si>
+    <t>H3.jpg</t>
+  </si>
+  <si>
     <t>食漁、樂漁、慢漁</t>
   </si>
   <si>
@@ -406,6 +418,9 @@
     <t>L4.png</t>
   </si>
   <si>
+    <t>H4.jpg</t>
+  </si>
+  <si>
     <t>樂天知命、安於樸實，打造「安居樂業」的未來願景</t>
   </si>
   <si>
@@ -457,6 +472,9 @@
     <t>L5.jpg</t>
   </si>
   <si>
+    <t>H5.jpg</t>
+  </si>
+  <si>
     <t>研發鳳梨全利用，宣揚惜食永續理念，保護社區生態環境</t>
   </si>
   <si>
@@ -502,6 +520,9 @@
     <t>L6.jpg</t>
   </si>
   <si>
+    <t>H6.webp</t>
+  </si>
+  <si>
     <t>土地平闊，地質肥沃，水利充足，人民富裕</t>
   </si>
   <si>
@@ -553,6 +574,9 @@
     <t>L7.jpg</t>
   </si>
   <si>
+    <t>H7.jpg</t>
+  </si>
+  <si>
     <t>台灣國境之南，境內氣候宜人四季如春，以農業及觀光為發展主力</t>
   </si>
   <si>
@@ -602,6 +626,9 @@
   </si>
   <si>
     <t>L8.png</t>
+  </si>
+  <si>
+    <t>H8.jpg</t>
   </si>
   <si>
     <t>以蓮霧種植和農村體驗為特色，積極推廣「透紅佳人」蓮霧品牌</t>
@@ -808,19 +835,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="B5:E11" displayName="Table_1" name="Table_1" id="1">
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="B5:F11" displayName="Table_1" name="Table_1" id="1">
+  <tableColumns count="5">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
     <tableColumn name="Column3" id="3"/>
     <tableColumn name="Column4" id="4"/>
+    <tableColumn name="Column5" id="5"/>
   </tableColumns>
   <tableStyleInfo name="工作表1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="AA5:AB11" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="AB5:AC11" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="2">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1030,20 +1058,20 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="3" width="32.38"/>
-    <col customWidth="1" min="4" max="4" width="38.0"/>
-    <col customWidth="1" min="5" max="5" width="26.63"/>
-    <col customWidth="1" min="6" max="6" width="14.13"/>
-    <col customWidth="1" min="7" max="7" width="134.88"/>
-    <col customWidth="1" min="11" max="11" width="14.5"/>
-    <col customWidth="1" min="12" max="12" width="78.75"/>
-    <col customWidth="1" min="13" max="13" width="10.38"/>
-    <col customWidth="1" min="14" max="14" width="10.63"/>
-    <col customWidth="1" min="15" max="15" width="52.88"/>
-    <col customWidth="1" min="16" max="16" width="20.38"/>
-    <col customWidth="1" min="17" max="17" width="16.5"/>
-    <col customWidth="1" min="18" max="18" width="75.13"/>
-    <col customWidth="1" min="21" max="21" width="49.88"/>
+    <col customWidth="1" min="2" max="4" width="32.38"/>
+    <col customWidth="1" min="5" max="5" width="38.0"/>
+    <col customWidth="1" min="6" max="6" width="26.63"/>
+    <col customWidth="1" min="7" max="7" width="14.13"/>
+    <col customWidth="1" min="8" max="8" width="134.88"/>
+    <col customWidth="1" min="12" max="12" width="14.5"/>
+    <col customWidth="1" min="13" max="13" width="78.75"/>
+    <col customWidth="1" min="14" max="14" width="10.38"/>
+    <col customWidth="1" min="15" max="15" width="10.63"/>
+    <col customWidth="1" min="16" max="16" width="52.88"/>
+    <col customWidth="1" min="17" max="17" width="20.38"/>
+    <col customWidth="1" min="18" max="18" width="16.5"/>
+    <col customWidth="1" min="19" max="19" width="75.13"/>
+    <col customWidth="1" min="22" max="22" width="49.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1056,7 +1084,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1130,80 +1158,81 @@
       </c>
       <c r="AB1" s="1" t="s">
         <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="6" t="s">
         <v>37</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="3">
         <v>220.0</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="6" t="s">
         <v>42</v>
       </c>
       <c r="R2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" s="3">
         <v>180.0</v>
       </c>
-      <c r="T2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="U2" s="6" t="s">
+      <c r="U2" s="3" t="s">
         <v>45</v>
       </c>
       <c r="V2" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="W2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="X2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="Y2" s="3" t="s">
+      <c r="Y2" s="6" t="s">
         <v>49</v>
       </c>
       <c r="Z2" s="3" t="s">
@@ -1214,80 +1243,81 @@
       </c>
       <c r="AB2" s="3" t="s">
         <v>52</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="3"/>
+      <c r="E3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="6" t="s">
         <v>62</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N3" s="3">
         <v>250.0</v>
       </c>
-      <c r="N3" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="P3" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" s="6" t="s">
         <v>67</v>
       </c>
       <c r="R3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="T3" s="3">
         <v>190.0</v>
       </c>
-      <c r="T3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="3" t="s">
         <v>70</v>
       </c>
       <c r="V3" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="W3" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="X3" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Y3" s="6" t="s">
         <v>74</v>
       </c>
       <c r="Z3" s="3" t="s">
@@ -1298,598 +1328,625 @@
       </c>
       <c r="AB3" s="3" t="s">
         <v>77</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="H4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>85</v>
+      </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="M4" s="5">
+      <c r="K4" s="3"/>
+      <c r="L4" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N4" s="5">
         <v>200.0</v>
       </c>
-      <c r="N4" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3" t="s">
+      <c r="O4" s="8" t="s">
         <v>88</v>
       </c>
+      <c r="P4" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q4" s="3"/>
       <c r="R4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="S4" s="5">
+        <v>90</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="T4" s="5">
         <v>250.0</v>
       </c>
-      <c r="T4" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="U4" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="V4" s="3"/>
-      <c r="W4" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="X4" s="10" t="s">
+      <c r="V4" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="Y4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y4" s="10" t="s">
+        <v>95</v>
+      </c>
       <c r="Z4" s="3"/>
-      <c r="AA4" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB4" s="7" t="s">
-        <v>81</v>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC4" s="7" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5" s="13" t="s">
         <v>98</v>
       </c>
+      <c r="D5" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>100</v>
+      </c>
       <c r="F5" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="H5" s="12"/>
+        <v>101</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>103</v>
+      </c>
       <c r="I5" s="12"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="M5" s="13">
+      <c r="K5" s="12"/>
+      <c r="L5" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="N5" s="13">
         <v>70.0</v>
       </c>
-      <c r="N5" s="13" t="s">
-        <v>103</v>
-      </c>
       <c r="O5" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="11" t="s">
-        <v>105</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="P5" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q5" s="12"/>
       <c r="R5" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="S5" s="13">
+        <v>108</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="T5" s="13">
         <v>160.0</v>
       </c>
-      <c r="T5" s="13" t="s">
-        <v>107</v>
-      </c>
       <c r="U5" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="V5" s="12"/>
-      <c r="W5" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="X5" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="Y5" s="12"/>
+      <c r="V5" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="W5" s="12"/>
+      <c r="X5" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y5" s="16" t="s">
+        <v>113</v>
+      </c>
       <c r="Z5" s="12"/>
-      <c r="AA5" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="AB5" s="14" t="s">
+      <c r="AA5" s="12"/>
+      <c r="AB5" s="12" t="s">
         <v>97</v>
+      </c>
+      <c r="AC5" s="14" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="F6" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="H6" s="17"/>
+      <c r="E6" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>121</v>
+      </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
-      <c r="K6" s="17" t="s">
+      <c r="K6" s="17"/>
+      <c r="L6" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="N6" s="5">
+        <v>300.0</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="T6" s="5">
+        <v>150.0</v>
+      </c>
+      <c r="U6" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="W6" s="17"/>
+      <c r="X6" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y6" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z6" s="17"/>
+      <c r="AA6" s="17"/>
+      <c r="AB6" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC6" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="M6" s="5">
-        <v>300.0</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="S6" s="5">
-        <v>150.0</v>
-      </c>
-      <c r="T6" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="U6" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="V6" s="17"/>
-      <c r="W6" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="X6" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y6" s="17"/>
-      <c r="Z6" s="17"/>
-      <c r="AA6" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="AB6" s="4" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>136</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="H7" s="12"/>
+        <v>137</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>139</v>
+      </c>
       <c r="I7" s="12"/>
       <c r="J7" s="12"/>
-      <c r="K7" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="L7" s="11" t="s">
+      <c r="K7" s="12"/>
+      <c r="L7" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="N7" s="13">
+        <v>200.0</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="P7" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="S7" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="T7" s="13">
+        <v>400.0</v>
+      </c>
+      <c r="U7" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="V7" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="W7" s="12"/>
+      <c r="X7" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y7" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="Z7" s="12"/>
+      <c r="AA7" s="12"/>
+      <c r="AB7" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="AC7" s="14" t="s">
         <v>136</v>
-      </c>
-      <c r="M7" s="13">
-        <v>200.0</v>
-      </c>
-      <c r="N7" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="O7" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="R7" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="S7" s="13">
-        <v>400.0</v>
-      </c>
-      <c r="T7" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="U7" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="V7" s="12"/>
-      <c r="W7" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="X7" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y7" s="12"/>
-      <c r="Z7" s="12"/>
-      <c r="AA7" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB7" s="14" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="H8" s="17"/>
+        <v>152</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>156</v>
+      </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
-      <c r="K8" s="17" t="s">
+      <c r="K8" s="17"/>
+      <c r="L8" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="N8" s="5">
+        <v>150.0</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="T8" s="5">
+        <v>230.0</v>
+      </c>
+      <c r="U8" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="W8" s="17"/>
+      <c r="X8" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y8" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z8" s="17"/>
+      <c r="AA8" s="17"/>
+      <c r="AB8" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="M8" s="5">
-        <v>150.0</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17" t="s">
+      <c r="AC8" s="7" t="s">
         <v>154</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="S8" s="5">
-        <v>230.0</v>
-      </c>
-      <c r="T8" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="V8" s="17"/>
-      <c r="W8" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="X8" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y8" s="17"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="AB8" s="7" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>164</v>
+        <v>168</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>170</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="H9" s="12"/>
+        <v>171</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>173</v>
+      </c>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
-      <c r="K9" s="12" t="s">
+      <c r="K9" s="12"/>
+      <c r="L9" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="N9" s="13">
+        <v>38.0</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="P9" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="S9" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="T9" s="13">
+        <v>38.0</v>
+      </c>
+      <c r="U9" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="V9" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="W9" s="12"/>
+      <c r="X9" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y9" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z9" s="12"/>
+      <c r="AA9" s="12"/>
+      <c r="AB9" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="L9" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="M9" s="13">
-        <v>38.0</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="O9" s="13" t="s">
+      <c r="AC9" s="14" t="s">
         <v>170</v>
-      </c>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="R9" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="S9" s="13">
-        <v>38.0</v>
-      </c>
-      <c r="T9" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="U9" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="V9" s="12"/>
-      <c r="W9" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="X9" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="Y9" s="12"/>
-      <c r="Z9" s="12"/>
-      <c r="AA9" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="AB9" s="14" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H10" s="17"/>
+        <v>186</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>191</v>
+      </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
-      <c r="K10" s="3" t="s">
-        <v>184</v>
-      </c>
+      <c r="K10" s="17"/>
       <c r="L10" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="N10" s="5">
+        <v>45.0</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="T10" s="5">
+        <v>120.0</v>
+      </c>
+      <c r="U10" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="W10" s="17"/>
+      <c r="X10" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="Y10" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z10" s="17"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="M10" s="5">
-        <v>45.0</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17" t="s">
+      <c r="AC10" s="7" t="s">
         <v>188</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="S10" s="5">
-        <v>120.0</v>
-      </c>
-      <c r="T10" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="U10" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="V10" s="17"/>
-      <c r="W10" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="X10" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="Y10" s="17"/>
-      <c r="Z10" s="17"/>
-      <c r="AA10" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB10" s="7" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>198</v>
+        <v>204</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>206</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="H11" s="12"/>
+        <v>207</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>209</v>
+      </c>
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
-      <c r="K11" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="M11" s="13">
+      <c r="K11" s="12"/>
+      <c r="L11" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="N11" s="13">
         <v>200.0</v>
       </c>
-      <c r="N11" s="13" t="s">
-        <v>203</v>
-      </c>
       <c r="O11" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="19"/>
+        <v>212</v>
+      </c>
+      <c r="P11" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q11" s="12"/>
       <c r="R11" s="19"/>
       <c r="S11" s="19"/>
       <c r="T11" s="19"/>
-      <c r="U11" s="12"/>
+      <c r="U11" s="19"/>
       <c r="V11" s="12"/>
-      <c r="W11" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="X11" s="16" t="s">
+      <c r="W11" s="12"/>
+      <c r="X11" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="Y11" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z11" s="12"/>
+      <c r="AA11" s="12"/>
+      <c r="AB11" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="AC11" s="14" t="s">
         <v>206</v>
-      </c>
-      <c r="Y11" s="12"/>
-      <c r="Z11" s="12"/>
-      <c r="AA11" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="AB11" s="14" t="s">
-        <v>197</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="H2"/>
-    <hyperlink r:id="rId2" ref="J2"/>
-    <hyperlink r:id="rId3" ref="O2"/>
-    <hyperlink r:id="rId4" ref="P2"/>
-    <hyperlink r:id="rId5" ref="U2"/>
-    <hyperlink r:id="rId6" ref="V2"/>
-    <hyperlink r:id="rId7" ref="X2"/>
-    <hyperlink r:id="rId8" ref="H3"/>
-    <hyperlink r:id="rId9" ref="J3"/>
-    <hyperlink r:id="rId10" ref="O3"/>
-    <hyperlink r:id="rId11" ref="P3"/>
-    <hyperlink r:id="rId12" ref="U3"/>
-    <hyperlink r:id="rId13" ref="V3"/>
-    <hyperlink r:id="rId14" ref="X3"/>
-    <hyperlink r:id="rId15" ref="X4"/>
-    <hyperlink r:id="rId16" ref="X5"/>
-    <hyperlink r:id="rId17" ref="X6"/>
-    <hyperlink r:id="rId18" ref="X7"/>
-    <hyperlink r:id="rId19" ref="X8"/>
-    <hyperlink r:id="rId20" ref="X9"/>
-    <hyperlink r:id="rId21" ref="X10"/>
-    <hyperlink r:id="rId22" ref="X11"/>
+    <hyperlink r:id="rId1" ref="I2"/>
+    <hyperlink r:id="rId2" ref="K2"/>
+    <hyperlink r:id="rId3" ref="P2"/>
+    <hyperlink r:id="rId4" ref="Q2"/>
+    <hyperlink r:id="rId5" ref="V2"/>
+    <hyperlink r:id="rId6" ref="W2"/>
+    <hyperlink r:id="rId7" ref="Y2"/>
+    <hyperlink r:id="rId8" ref="I3"/>
+    <hyperlink r:id="rId9" ref="K3"/>
+    <hyperlink r:id="rId10" ref="P3"/>
+    <hyperlink r:id="rId11" ref="Q3"/>
+    <hyperlink r:id="rId12" ref="V3"/>
+    <hyperlink r:id="rId13" ref="W3"/>
+    <hyperlink r:id="rId14" ref="Y3"/>
+    <hyperlink r:id="rId15" ref="Y4"/>
+    <hyperlink r:id="rId16" ref="Y5"/>
+    <hyperlink r:id="rId17" ref="Y6"/>
+    <hyperlink r:id="rId18" ref="Y7"/>
+    <hyperlink r:id="rId19" ref="Y8"/>
+    <hyperlink r:id="rId20" ref="Y9"/>
+    <hyperlink r:id="rId21" ref="Y10"/>
+    <hyperlink r:id="rId22" ref="Y11"/>
   </hyperlinks>
   <drawing r:id="rId23"/>
   <tableParts count="2">
